--- a/quizzes/022_programming_language_debug_quiz--quizzes.xlsx
+++ b/quizzes/022_programming_language_debug_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'JavaScript'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'python'}</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Python'}</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c++'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C++'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'JavaScript'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'c++'}</t>
+          <t>c++</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'C++'}</t>
+          <t>C++</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'java'}</t>
+          <t>java</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Java'}</t>
+          <t>Java</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "Bachelor's Degree"}</t>
+          <t>Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': "Master's Degree"}</t>
+          <t>Master's Degree</t>
         </is>
       </c>
     </row>
